--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488240_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488240_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4385</v>
+        <v>4.9232</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9726</v>
+        <v>1.408</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4659</v>
+        <v>3.5151</v>
       </c>
       <c r="G2" t="n">
         <v>2.6563</v>
@@ -610,13 +610,13 @@
         <v>2.2234</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0797</v>
+        <v>1.5644</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5259</v>
+        <v>0.9613</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5538</v>
+        <v>0.6031</v>
       </c>
       <c r="V2" t="n">
         <v>1.2583</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3311</v>
+        <v>4.8274</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7724</v>
+        <v>2.121</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5587</v>
+        <v>2.7064</v>
       </c>
       <c r="G3" t="n">
         <v>2.3968</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1196</v>
+        <v>0.6159</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0709</v>
+        <v>0.2776</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1905</v>
+        <v>0.3382</v>
       </c>
       <c r="V3" t="n">
         <v>1.2589</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2458</v>
+        <v>3.2765</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6127</v>
+        <v>1.5695</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6331</v>
+        <v>1.707</v>
       </c>
       <c r="G4" t="n">
         <v>0.3584</v>
@@ -766,13 +766,13 @@
         <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5168</v>
+        <v>0.5475</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1816</v>
+        <v>0.1384</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3352</v>
+        <v>0.4091</v>
       </c>
       <c r="V4" t="n">
         <v>1.2589</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1203</v>
+        <v>1.5548</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4593</v>
+        <v>-1.1973</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5797</v>
+        <v>2.752</v>
       </c>
       <c r="G5" t="n">
         <v>2.7973</v>
@@ -844,13 +844,13 @@
         <v>1.6676</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3972</v>
+        <v>0.8316</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0349</v>
+        <v>0.2969</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3623</v>
+        <v>0.5347</v>
       </c>
       <c r="V5" t="n">
         <v>-1.8888</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>V. PIETUKHOV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0585</v>
+        <v>-0.1269</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4189</v>
+        <v>-0.1115</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4774</v>
+        <v>-0.0153</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8114</v>
+        <v>0.9271</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5179</v>
+        <v>-0.2234</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7065</v>
+        <v>1.1505</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2708</v>
+        <v>0.8628</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1465</v>
+        <v>0.1885</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8756</v>
+        <v>0.6742</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5406</v>
+        <v>0.0643</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3715</v>
+        <v>-0.412</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1692</v>
+        <v>0.4763</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.8529</v>
+        <v>0.3706</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8529</v>
+        <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4144</v>
+        <v>0.4632</v>
       </c>
       <c r="T7" t="n">
-        <v>1.016</v>
+        <v>-0.0479</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3984</v>
+        <v>0.5111</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3144</v>
+        <v>-1.8877</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3144</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BOTELLO GARCIA</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.47</v>
+        <v>-0.4683</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0553</v>
+        <v>-2.995</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4147</v>
+        <v>2.5267</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4147</v>
+        <v>0.8114</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2.5179</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4147</v>
+        <v>-1.7065</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.2708</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.1465</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.8756</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4147</v>
+        <v>0.5406</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.3715</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4147</v>
+        <v>0.1692</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0547</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0547</v>
+        <v>0.4399</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.4476</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0005</v>
+        <v>-0.3144</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. PIETUKHOV</t>
+          <t>A. BOTELLO GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8731</v>
+        <v>-0.47</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8085</v>
+        <v>-0.0553</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0646</v>
+        <v>-0.4147</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9271</v>
+        <v>-0.4147</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2234</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1505</v>
+        <v>-0.4147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8628</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1885</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6742</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0643</v>
+        <v>-0.4147</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.412</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4763</v>
+        <v>-0.4147</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.283</v>
+        <v>-0.0547</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7449</v>
+        <v>-0.0547</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4618</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8877</v>
+        <v>-0.0005</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0561</v>
+        <v>-1.3346</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5906</v>
+        <v>-3.5243</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5344</v>
+        <v>2.1897</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3505</v>
@@ -1234,13 +1234,13 @@
         <v>2.594</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7238</v>
+        <v>1.4453</v>
       </c>
       <c r="T10" t="n">
-        <v>0.73</v>
+        <v>0.7962</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9938</v>
+        <v>0.6491</v>
       </c>
       <c r="V10" t="n">
         <v>3.4616</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7819</v>
+        <v>-1.7458</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0139</v>
+        <v>-1.0024</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.768</v>
+        <v>-0.7433</v>
       </c>
       <c r="G11" t="n">
         <v>-0.727</v>
@@ -1312,13 +1312,13 @@
         <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1284</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0386</v>
+        <v>0.0501</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0537</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8883</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7971</v>
+        <v>-3.1259</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8822</v>
+        <v>-2.9893</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.1366</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9143</v>
@@ -1390,13 +1390,13 @@
         <v>0.9264</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0682</v>
+        <v>0.6031</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3743</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3061</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8883</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.160099999999998</v>
+        <v>8.254499999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.9269</v>
+        <v>-5.8325</v>
       </c>
       <c r="F13" t="n">
-        <v>14.0869</v>
+        <v>14.087</v>
       </c>
       <c r="G13" t="n">
         <v>6.484900000000001</v>
@@ -1468,13 +1468,13 @@
         <v>13.8964</v>
       </c>
       <c r="S13" t="n">
-        <v>5.9379</v>
+        <v>7.032300000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2822</v>
+        <v>3.3764</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6556</v>
+        <v>3.6557</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6303000000000005</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5203</v>
+        <v>3.3004</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8467</v>
+        <v>0.1612</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6736</v>
+        <v>3.1392</v>
       </c>
       <c r="G14" t="n">
         <v>2.552</v>
@@ -1546,13 +1546,13 @@
         <v>2.7793</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0244</v>
+        <v>-0.1955</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4266</v>
+        <v>-0.2589</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4022</v>
+        <v>0.0634</v>
       </c>
       <c r="V14" t="n">
         <v>0.9439</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6966</v>
+        <v>2.8219</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7011</v>
+        <v>0.9176</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9955000000000001</v>
+        <v>1.9043</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3535</v>
@@ -1624,13 +1624,13 @@
         <v>3.5205</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6315</v>
+        <v>-0.5061</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.0224</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4373</v>
+        <v>-0.5285</v>
       </c>
       <c r="V15" t="n">
         <v>2.0139</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1179</v>
+        <v>1.5262</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8928</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0107</v>
+        <v>2.321</v>
       </c>
       <c r="G16" t="n">
         <v>-3.9503</v>
@@ -1702,13 +1702,13 @@
         <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8177</v>
+        <v>-0.4094</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5546</v>
+        <v>-0.4567</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2632</v>
+        <v>0.0472</v>
       </c>
       <c r="V16" t="n">
         <v>4.2183</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3738</v>
+        <v>0.4883</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6365</v>
+        <v>1.4406</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2627</v>
+        <v>-0.9523</v>
       </c>
       <c r="G18" t="n">
         <v>2.4875</v>
@@ -1858,13 +1858,13 @@
         <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3377</v>
+        <v>-0.2232</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0584</v>
+        <v>-0.2543</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2793</v>
+        <v>0.0311</v>
       </c>
       <c r="V18" t="n">
         <v>-2.5172</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.031</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.192</v>
+        <v>-0.0941</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.839</v>
+        <v>-0.7995</v>
       </c>
       <c r="G19" t="n">
         <v>1.133</v>
@@ -1936,13 +1936,13 @@
         <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5693</v>
+        <v>-0.4318</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9849</v>
+        <v>-0.8869</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4156</v>
+        <v>0.4551</v>
       </c>
       <c r="V19" t="n">
         <v>-2.7065</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DIAZ MACIAS</t>
+          <t>P. CORREA GALLARDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7823</v>
+        <v>-1.9577</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.1905</v>
+        <v>-2.1996</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4082</v>
+        <v>0.2419</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.671</v>
+        <v>-3.076</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.178</v>
+        <v>-0.8809</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.493</v>
+        <v>-2.1951</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.1467</v>
+        <v>-1.7361</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.354</v>
+        <v>0.1288</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.7927</v>
+        <v>-1.865</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5242</v>
+        <v>-1.3398</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.824</v>
+        <v>-1.0097</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2997</v>
+        <v>-0.3301</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5558999999999999</v>
+        <v>1.8529</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1499</v>
+        <v>1.8529</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5001</v>
+        <v>-0.7346</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2263</v>
+        <v>-0.4635</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7264</v>
+        <v>-0.2711</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9444</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CORREA GALLARDO</t>
+          <t>A. DIAZ MACIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0939</v>
+        <v>-3.0067</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8851</v>
+        <v>-5.0925</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2087</v>
+        <v>2.0859</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.076</v>
+        <v>-3.671</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8809</v>
+        <v>-2.178</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1951</v>
+        <v>-1.493</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7361</v>
+        <v>-3.1467</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1288</v>
+        <v>-1.354</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.865</v>
+        <v>-1.7927</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3398</v>
+        <v>-0.5242</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0097</v>
+        <v>-0.824</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3301</v>
+        <v>0.2997</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8529</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8529</v>
+        <v>3.1499</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8708</v>
+        <v>0.2758</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.149</v>
+        <v>-0.1284</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7218</v>
+        <v>0.4041</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.9444</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9631</v>
+        <v>-3.5628</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0851</v>
+        <v>-3.8893</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1221</v>
+        <v>0.3265</v>
       </c>
       <c r="G22" t="n">
         <v>-0.006</v>
@@ -2170,13 +2170,13 @@
         <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7678</v>
+        <v>-0.3675</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.766</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0018</v>
+        <v>0.2027</v>
       </c>
       <c r="V22" t="n">
         <v>-2.0776</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6205</v>
+        <v>-3.8869</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6478</v>
+        <v>-5.1581</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0272</v>
+        <v>1.2712</v>
       </c>
       <c r="G23" t="n">
         <v>-2.223</v>
@@ -2248,13 +2248,13 @@
         <v>2.0382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4676</v>
+        <v>-0.734</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.149</v>
+        <v>-0.6594</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3186</v>
+        <v>-0.0746</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1888</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.160099999999999</v>
+        <v>-4.548800000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.0869</v>
+        <v>-14.087</v>
       </c>
       <c r="F24" t="n">
-        <v>6.926899999999999</v>
+        <v>9.5382</v>
       </c>
       <c r="G24" t="n">
         <v>-6.4852</v>
@@ -2326,13 +2326,13 @@
         <v>18.5287</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.9379</v>
+        <v>-3.3263</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.6557</v>
+        <v>-3.6558</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.2822</v>
+        <v>0.3294</v>
       </c>
       <c r="V24" t="n">
         <v>0.6304</v>
